--- a/seo/URL_INSPECTION.xlsx
+++ b/seo/URL_INSPECTION.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/reduce-image-size-in-kb-online-free.html</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,7 +510,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-200kb-online-free.html</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -532,7 +530,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-20kb-online-free.html</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -553,7 +550,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/signature-resize-online-free-10-20-kb.html</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -574,7 +570,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-photo-for-pan-card-online-free.html</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -595,7 +590,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/kb-to-mb-converter-and-mb-to-kb-both.html</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -616,7 +610,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/home-loan-emi-calculator-with.html</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -637,7 +630,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/sip-calculator-estimate-your-mutual.html</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -658,7 +650,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/income-tax-calculator-fy-2026-27-new-vs.html</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -679,7 +670,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/gst-calculator-2026-add-or-remove-gst.html</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -700,7 +690,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-100kb-online-free-scans.html</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -721,7 +710,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-500kb-online-free-gst.html</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -742,7 +730,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-300kb-online-free-neet.html</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -763,7 +750,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-1mb-online-free-under-1.html</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -784,7 +770,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-50kb-online-free-photo.html</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -805,7 +790,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-100kb-online-free.html</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -826,7 +810,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-200kb-online-free.html</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -847,7 +830,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-cm-online-free-cm-mm-or.html</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -868,7 +850,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/jpg-to-pdf-under-200kb-online-free-also.html</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -889,7 +870,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/ppf-epf-sukanya-samriddhi-fd-and-rd.html</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -910,7 +890,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/free-passport-and-visa-photo-maker.html</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -931,7 +910,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/exam-photo-and-signature-resizer-exact.html</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -952,7 +930,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/merge-split-and-reorder-pdfs-free.html</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -973,7 +950,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-mask-your-aadhaar-or-pan-before.html</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -994,7 +970,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/us-visa-and-dv-lottery-photo-600x600.html</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1015,7 +990,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/convert-heic-to-jpg-shrink-photos-and.html</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1036,7 +1010,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/what-is-good-cibil-score-how-to-check.html</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1057,7 +1030,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/how-much-cash-can-i-carry-on.html</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1078,7 +1050,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-50kb-online-free-sharp.html</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1099,7 +1070,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-2mb-online-free-aadhaar.html</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1120,7 +1090,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-10kb-online-free-photo.html</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1141,7 +1110,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-15kb-online-free-photo.html</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1162,7 +1130,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-30kb-online-free-photo.html</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1183,7 +1150,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-500kb-online-free.html</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1204,7 +1170,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-150kb-online-free.html</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1225,7 +1190,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/can-i-take-codeine-sleeping-pills-or.html</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1246,7 +1210,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/do-i-pay-tax-on-money-sent-from-abroad.html</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1267,7 +1230,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/how-much-emergency-fund-do-you-need.html</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1288,7 +1250,6 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/free-resume-builder-with-free-pdf.html</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1309,7 +1270,5067 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/free-upi-qr-code-generator-make-scan.html</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Australian Passport Photo Size: 35-40 x 45-50 mm (Free Maker)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/australian-passport-photo-size-35-40-x.html</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Cheapest Countries to Retire Abroad on $2,000 a Month</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/best-countries-to-retire-abroad-on-2000.html</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Canadian Passport Photo Size: 50x70 mm Rules (Free Photo Maker)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/canadian-passport-photo-size-50x70-mm.html</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Career Guide: Work Smarter, Avoid Burnout and Grow (Start Here)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/career-guide-work-smarter-avoid-burnout.html</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>China Visa Photo Size: 33x48 mm and 354x472 Digital (Free Maker)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/china-visa-photo-size-33x48-mm-and.html</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Compare Countries 2026: Wages, Tax, Mortgages and Pensions</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/compare-countries-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Credit Card Payoff Calculator: How Long Will Your Debt Take?</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/credit-card-payoff-calculator-how-long.html</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Debt Consolidation Loans: When They Save Money (Calculator)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/debt-consolidation-loans-when-they-save.html</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Free Invoice Generator: No Sign-Up, No Watermark, PDF in Seconds</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/free-invoice-generator-no-sign-up-no.html</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Free Online Tools That Don't Upload Your Files or Need Sign-Up</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/free-online-tools-that-dont-upload-your.html</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Free QR Code Generator That Never Expires (No Sign-Up, No Trial)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/free-qr-code-generator-that-never.html</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Life Insurance Calculator: How Much Does Life Insurance Cost by Age?</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-much-does-life-insurance-cost-by.html</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Prediction Markets: How Kalshi and Polymarket Work and Are They Legal?</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-prediction-markets-like-kalshi-and.html</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>How to Buy SpaceX Stock and Other IPO Shares as a Small Investor</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-small-investors-can-buy-ipo-shares.html</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>How Much Car Can I Afford? Car Affordability Calculator for 2026</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-afford-car-in-2026-when-average.html</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>How to Explain a Gap in Employment or a Layoff in an Interview</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-explain-layoff-or-career-gap-in.html</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sign PDF Free: How to Sign a PDF Without an Account or Limits</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-sign-pdf-for-free-without.html</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Income Tax by Country 2026: Countries With the Lowest Income Tax</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/income-tax-by-country-2026-how-much-of.html</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>9</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Countries With No Inheritance Tax and Rates by Country 2026</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/inheritance-tax-by-country-2026.html</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>10</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Will Interest Rates Go Up? 7 Money Moves to Make Now</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/interest-rates-are-rising-again-7-money.html</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Gold Price Fall 2026: Is Gold Still a Safe Haven?</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/is-gold-still-safe-haven-after-its-big.html</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Electric Car vs Petrol Cost: Is an EV Cheaper to Run? (Calculator)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/is-it-cheaper-to-charge-ev-or-fill-up.html</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>What Jobs Will AI Replace in 2026, and Which Skills Keep You Safe?</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/jobs-ai-is-replacing-in-2026-and-skills.html</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Lump Sum or Monthly Pension: Which Should You Take? (Calculator)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/lump-sum-or-monthly-pension-which.html</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Meeting Time Zone Planner: Find a Time That Works in Every City</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/meeting-time-zone-planner-find-time.html</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Self-Improvement and Mental Well-Being: A Practical Guide (Start Here)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/mental-well-being-and-self-improvement.html</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Minimum Wage by Country 2026: Hourly and Monthly Rates in US Dollars</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/minimum-wage-by-country-2026-hourly-and.html</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Mortgage Rates by Country 2026: Where Buying a Home Costs the Most</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/mortgage-rates-by-country-2026-where.html</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>9</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OCI Photo Size: Square JPEG Under 200 KB (Free Photo Maker)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/oci-photo-size-square-jpeg-under-200-kb.html</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Personal Finance for Beginners: A Step-by-Step Guide (Start Here)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/personal-finance-for-beginners-step-by.html</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Retirement Age by Country 2026, Including Retirement Age in Europe</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/retirement-age-by-country-2026-state.html</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Salary Increase 2027 Forecasts by Country: Every Major Survey</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/salary-increase-forecasts-2027-by.html</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Schengen Visa Photo Size: 35x45 mm, Face 32-36 mm (Free Photo Maker)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/schengen-visa-photo-size-35x45-mm-face.html</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Rent or Buy? Rent vs Buy Calculator With Mortgage Rates Above 7%</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/should-you-buy-house-with-mortgage.html</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>5</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Stablecoins Explained: Can You Earn Interest on Digital Dollars?</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/stablecoins-explained-can-you-really.html</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>6</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Average Pension by Country 2026: State Pension Amounts Compared</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/state-pension-amounts-by-country-2026.html</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>7</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Strong Password and Passphrase Generator, Plus a Safe Breach Check</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/strong-password-and-passphrase.html</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>8</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Subscription Tracker: Find Forgotten Subscriptions Before They Renew</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/subscription-tracker-find-forgotten.html</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>9</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>UK Passport Photo Size: 35x45 mm Print and Digital Rules (Free)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/uk-passport-photo-size-35x45-mm-print.html</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>10</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>US Passport Photo Requirements and Size: Make a 2x2 Photo Free at Home</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/us-passport-photo-size-and-rules-make.html</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>What Happens If a Bank Fails? Your Money if a Bank or App Goes Bust</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/what-happens-to-your-money-if-your-bank.html</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Digital Legacy: Your Online Accounts and Crypto When You Die</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/what-happens-to-your-online-accounts.html</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Raise Calculator: What Is a Fair Pay Raise in 2026 After Inflation?</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/what-is-fair-pay-raise-in-2026-how-to.html</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>What Is GDP? Its Role in Measuring an Economy, Explained</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/what-is-gdp-its-role-in-measuring.html</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Best Place to Keep Cash When Rates Rise: Savings, T-Bills or Funds</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/where-to-keep-your-cash-when-rates-rise.html</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Why Are Groceries and Prices So Expensive When Inflation Is Down?</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/why-are-prices-still-so-high-when.html</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>7</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Why Did My Car Insurance Go Up When I Never Made a Claim?</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/why-did-my-insurance-premium-go-up-when.html</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>10-Year Treasury Yield Above 5%: Why, and What It Means for You</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/why-is-10-year-treasury-yield-above-5.html</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>9</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Credit Karma vs FICO: Why Is My Credit Score Different on Every App?</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/why-is-my-credit-score-different-on.html</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Character Counter and Word Counter With Limits for X, LinkedIn and SMS</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/word-counter-with-character-limits-for.html</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CEO vs COO: Roles, Responsibilities and Key Differences</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/ceo-vs-coo.html</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>How the Election System in India Works</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/election-system-in-india.html</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>3</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>How US Elections Work: The Election System Explained Simply</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/election-system-in-united-states.html</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>4</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>How to Become a Fashion Designer: A Career Guide</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/fashion-designing.html</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>5</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Financial Independence: How to Achieve It Step by Step</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/financial-independence.html</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>6</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>How Do You Know When Someone Really Loves You?</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-do-you-know-when-someone-really.html</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>7</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>How to Be Happy: Simple Habits for a Happier Life</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-be-happy.html</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>8</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>How to Control Diabetes Naturally: Diet and Lifestyle Tips</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-control-diabetes.html</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>9</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>How to Get Over Someone and Move On After a Breakup</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-forgot-someone.html</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>10</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>How to Stop Being Shy: Overcoming Shyness as an Introvert</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-overcome-introvert-shyness.html</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>How to Fall Asleep Fast: Simple Ways to Sleep Peacefully</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-sleep-fastly-and-peacefully.html</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Is Fate Real? Destiny vs Free Will Explained</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/is-fate-is-true.html</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Lesser-Known Facts About Joe Biden</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/unknown-facts-of-joe-biden.html</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>What Are Altcoins? Alternative Cryptocurrencies Explained</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/what-are-altcoins.html</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>5</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Corporate Life Lessons: The Biggest Lessons From the Corporate World</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/what-are-biggest-lessons-you-have.html</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>6</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>What Is Karma? Meaning, Types and How It Works</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/what-is-karma.html</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>7</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Australia vs Canada: Which Is Better to Live In?</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/which-is-better-country-to-live-in.html</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>8</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>USA vs UK: Which Country Is Better to Live In?</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/which-is-better-to-live-in-usa-or-uk.html</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>9</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Why Is Dubai Called A Fake City?</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/why-is-dubai-called-fake-city.html</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>10</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Why Is the US So Rich? Why America Is Wealthier Than Other Countries</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/why-is-united-states-of-america-so-much.html</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Deep Work vs Shallow Work: How to Focus Better</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/deep-work-vs-shallow-work.html</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>2</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>FIRE Movement: Financial Independence, Retire Early Explained</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/financial-independence-retire-earlyfire.html</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>3</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>How to Increase Positive Thoughts: Practical Tips</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/how-to-increase-positive-thoughts.html</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>4</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>How to Learn Anything Fast: Proven Techniques</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/how-to-learn-anything-fast.html</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>5</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Workplace Relationships: How to Keep Good Relations at Work</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/how-to-maintain-good-relation-in-work.html</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>6</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>What Is Inflation? Causes, Types and Effects Explained</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/inflation-tutorial.html</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>7</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Mutual Funds vs Stocks and Day Trading: Which Is Better?</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/mutual-funds-vs-stocks.html</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>8</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Qualities of a Good Team Leader</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/qualities-of-good-team-lead.html</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>9</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Oxford University Facts: Lesser-Known Facts About Oxford</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/unknown-facts-of-university-of-oxford.html</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Day 12</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>10</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>How to Control Your Emotions: Practical Tips</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/08/how-to-control-emotions.html</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>How to Manage Credit Card Debt Wisely</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/08/how-to-manage-credit-card-loans.html</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>What Is IQ? Intelligence Quotient Explained</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/08/intelligence-quotient-blog.html</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>3</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Is Investing in Cryptocurrency Safe?</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/08/is-invest-in-cryptocurrency-is-safe.html</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>4</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Bitcoin Crash: Why Bitcoin Prices Fall</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/08/what-is-bitcoin-crash.html</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>5</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence vs Machine Learning: Key Differences</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/comparing-artificial-intelligence-vs.html</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>6</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>How Much Does Google Know About You?</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/how-much-does-google-know-about-me.html</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>7</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Standard Deduction 2026 and Other US Tax Deductions Explained</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/income-tax-exemptions-in-united-states.html</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>8</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Floating Interest Rate Home Loan: Is a Floating Rate Good for You?</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/is-floating-interest-is-good-for-house.html</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>9</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Is Investing in Gold a Good Idea?</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/is-invest-in-gold-is-good-idea.html</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Day 13</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>10</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SIP vs Lumpsum: Which Is Better in Mutual Funds?</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/lumpsum-vs-sip-mutual-fund-which-is-best.html</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>What Is Mature Love? The Definition of Mature Love, Explained</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/what-is-mature-love-definition-of.html</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>What Is a 401(k) and How Does It Work? A Complete Guide</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/a-comprehensive-guide-401k.html</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>3</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>What Is an Alpha Male? Traits and Myths</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/all-about-alpha-male.html</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>4</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Can Money Really Buy Happiness?</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/can-money-really-buy-happiness-what-can.html</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>5</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Data Structures: Why They Matter in Programming</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/data-structures-why-it-matters-and-how.html</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>6</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Hedging in Finance: A Complete Guide</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/hedging-in-financea-comprehensive-guide.html</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>7</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>How Does Google Search Work? The Algorithm Behind the Results</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/how-googles-algorithm-works-science.html</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>8</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Compassion Fatigue: Signs, Causes and How to Recover</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/how-to-cure-compassion-fatigue-guide-to.html</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>9</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Behavioral Finance and Investor Psychology Explained</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/investor-psychology-behavioral-finance.html</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Day 14</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>10</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>When to Quit Your Job: 6 Signs It Is Time</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/the-6-signs-you-need-to-quit-your-job.html</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Day 15</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Annuities Explained: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/the-ultimate-guide-to-annuities-what.html</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Day 15</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>What Makes You Age Faster? The Worst Habits That Age You</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/the-worst-habits-that-age-you-what-you.html</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Day 15</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Dealing With Uncertainty: How to Cope When Things Are Unclear</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/uncertainty-isnt-always-bad-thing-how.html</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Day 15</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>4</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>What Is a Wormhole in Space? Explained Simply</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/what-is-warm-hole-in-space-just-what.html</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Day 15</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>5</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Is Data Science a Good Career? Why It Is the Next Big Thing in Jobs</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/why-data-science-is-emerging-field-next.html</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Day 15</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>6</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Why Politics Is Important: The Biggest Myths</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/why-politics-is-important-biggest-myths.html</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Day 15</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>7</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Life Lessons to Learn Before Age 30</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/12/lessons-should-be-learned-before-age-30.html</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Day 15</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>8</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Mental Toughness: How to Build Unbreakable Inner Strength</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/12/the-mental-toughness-guide-how-to.html</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Day 15</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>9</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Why Is French Important? What French Means to the World</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2021/12/what-does-french-language-mean-to-world.html</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Day 15</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>10</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Morning Routine for More Energy: Simple Steps for an Energetic Morning</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/do-these-steps-to-have-energetic-morning.html</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Day 16</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>How to Increase Your Chances of Success: Zen Quotes</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/how-to-increase-chances-of-success-zen.html</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Day 16</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>How to Increase Focus and Concentration</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/how-to-increase-focus-and-concentration.html</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Day 16</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>New Year Resolutions: How to Actually Keep Them, Step by Step</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/step-to-step-process-to-achieve-new.html</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Day 16</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>4</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Healthy Lifestyle Tips: Simple Steps to Improve Your Lifestyle</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/steps-to-improve-your-lifestyle.html</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Day 16</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>5</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>How to Be Successful in Life: 20 Steps to Win</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/steps-to-win-in-life.html</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Day 16</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>6</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ways to Raise Smarter Children</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/ways-to-raise-your-children-as-smarter.html</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Day 16</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>7</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>How to Be a Good Leader: 12 Rules of Leadership</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2022/02/grammar-of-good-leader.html</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Day 16</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>8</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>How to Become Rich: The Habits That Really Build Wealth</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2022/09/top-secrets-to-become-rich.html</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Day 16</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>9</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Biological Neural Network Explained (vs Artificial Neural Networks)</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/02/a-study-about-biological-neural-network.html</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Day 16</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>10</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Reconnaissance in Ethical Hacking: Footprinting Explained</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/02/reconnaissance-in-ethical-hacking.html</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Day 17</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Service Based Companies vs Product Based Companies: The Difference</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/a-study-about-service-and-product-based.html</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Day 17</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Effects of a Recession: How It Affects You and the Economy</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/a-study-on-recession-impact.html</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Day 17</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>3</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Forex Trading Explained: A Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/forex-study.html</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Day 17</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>4</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>How Is Currency Value Determined? How a Country's Currency Is Valued</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/how-currency-value-of-country-been.html</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Day 17</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>5</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>How to Find a Job in the UAE: A Complete Guide</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/how-to-find-job-in-united-arab-emirates.html</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Day 17</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>6</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>How to Socialize: Tips to Connect With People</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/how-to-socialize.html</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Day 17</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>7</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>NASDAQ 100 vs S&amp;P 500: Which Is Better?</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/nasdaq-100-vs-s-500.html</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Day 17</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>8</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Why Is Bitcoin Banned? Why Governments Ban or Restrict Bitcoin</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/reasons-on-why-governments-ban-bitcoins.html</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Day 17</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>9</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Time Zones Explained: How They Work</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/time-zones-study.html</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Day 17</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>10</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>What Happens When a Bank Fails?</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/what-happen-when-bank-fails.html</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Day 18</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Product Based Companies: What They Are and How They Work</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-about-product-based-companies.html</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Day 18</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>2</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Fixed vs Floating Interest Rate: Which Is Better?</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-fixed-interest-vs-floating.html</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Day 18</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>3</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Is an MBA Worth It? A Complete Guide</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-mba.html</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Day 18</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>4</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Tax Free Countries: Countries With No Income Tax</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-tax-free-nations.html</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Day 18</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>5</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Zen Quotes and Sayings: Classic Zen Quotes and Their Meaning</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-zen-quotes.html</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Day 18</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>6</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>How to Diversify Your Stock Portfolio</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/how-to-do-portfolio-diversification-in.html</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Day 18</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>7</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Life Satisfaction: How to Be More Satisfied With Your Life</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/how-to-improve-my-self-satisfaction.html</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Day 18</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>8</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>How to Reduce Stress at Work: Easing Mental Stress</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/how-to-reduce-mental-stress-at-work.html</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Day 18</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>9</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Is Online Education Good or Bad?</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/is-online-education-is-good-or-bad.html</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Day 18</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>10</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Finland Education System: Why It Is Considered the Best</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/why-finland-education-system-is.html</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Day 19</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Reducing Mental Stress: Strategies for a Healthier Mind</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/05/reducing-mental-stress-strategies-for.html</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Day 19</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>2</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Developing vs Developed Countries: Key Differences</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/classification-of-nations-developing-vs.html</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Day 19</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>3</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Living in the Present Moment: How to Live in the Present</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/embracing-present-art-of-living-in.html</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Day 19</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>4</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>How to Deal With Rejection: Building Resilience</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/embracing-resilience-strategies-to-face.html</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Day 19</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>How to Practice Mindfulness: A Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/how-to-attain-mindfulness.html</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Day 19</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>6</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>How to Cope With Losing Your Job</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/how-to-face-job-termination.html</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Day 19</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>7</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>How to Pay Off Credit Card Debt Fast</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/methods-to-efficiently-pay-off-credit.html</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Day 19</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>8</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Benefits of Working From Home: Why Professionals Love It</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/the-enchantment-of-work-from-home.html</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Day 19</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>9</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Constructive Criticism in Leadership: Why It Matters</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/the-essential-role-of-constructive.html</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Day 19</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>10</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Surround Yourself With Good People: Why Leaders Need Worthy People</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/the-leaders-alliance-with-worthy-men.html</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Day 20</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>The Psychology of Losing Money in the Stock Market</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/the-psychology-of-losing-money-in-stock.html</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Day 20</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>2</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Benefits of AI for Business: Why Companies Invest in AI</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/the-significance-of-artificial.html</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Day 20</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>3</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Why Do Companies Manufacture in China and East Asia?</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/why-developed-countries-want-to-open.html</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Day 20</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>4</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>How to Avoid Online Scams and Not Lose Money</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/write-various-headings-for-how-to-dont.html</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Day 20</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>5</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Breaking the Burnout Cycle: Work-Life Balance Tips</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/07/breaking-burnout-cycle-strategies-for.html</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Day 20</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>6</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Cost of Living Around the World: A Comparison</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/07/cost-of-living-comparison-across-world.html</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Day 20</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>7</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>From Casual to Serious: Moving a Relationship Forward</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/07/navigating-transition-from-casual-to.html</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Day 20</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>8</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Bad Boss Signs: How to Tell You Work for a Toxic Boss</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/07/recognizing-telltale-signs-of-working.html</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Day 20</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>9</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Unconditional Love: What It Means and How to Cultivate It</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/07/unconditional-love-what-it-means-and.html</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Day 20</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>10</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>How to Turn Thoughts Into Action</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/bridging-gap-transforming-thoughts-into.html</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Day 21</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>FIRE Movement: Financial Independence, Retire Early Explained</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/fire-financial-independence-retire.html</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Day 21</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Do Violent Movies Cause Violence? What the Research Says</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/lights-camera-action-and-reaction-link.html</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Day 21</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>3</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Portfolio Diversification Strategies for Long-Term Success</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/mastering-financial-portfolio.html</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Day 21</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>4</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Love in the Digital Age: How Technology Changes Love</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/normal-0-false-false-false-en-in-x-none.html</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Day 21</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>5</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Pursuit of Happiness: Strategies for a Fulfilling Life</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/pursuit-of-happiness-strategies-for.html</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Day 21</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>6</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>How to Become Indispensable at Work and Strengthen Your Position</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/strengthening-your-position-in-your-job.html</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Day 21</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>7</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Qualities of a Good Leader: The Leadership Qualities That Matter Most</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/the-desired-qualities-of-leadership.html</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Day 21</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>8</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>What Is the Petrodollar? The Petrodollar System Explained</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/the-genesis-of-petrodollars-unveiling.html</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Day 21</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>9</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>The Psychology of Fear: How the Brain Responds</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/the-psychology-of-fear-understanding.html</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Day 21</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>10</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>The Psychology of Love: What Makes Love Last</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/the-psychology-of-long-lasting-love.html</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>World Reserve Currency: Why the US Dollar Holds the Title</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/the-us-dollar-global-reserve-currency.html</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>The Power of Positivity: How Positive Thinking Helps</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/understanding-power-of-positivity.html</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>3</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Understanding Stress: The First Step to a Stress-Free Life</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/understanding-stress-first-step-to.html</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>4</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>What Does It Take to Be Courageous?</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/what-it-takes-to-be-courage.html</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>5</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Work-Life Balance: Balancing Ambition and Well-Being</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/work-life-balance-navigating.html</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>6</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>What Is Zen? Zen Buddhism, Mindfulness and Enlightenment Explained</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/zen-journey-into-essence-of-mindfulness.html</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>7</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Artificial Superintelligence: Myth or Inevitable Reality?</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/artificial-superintelligence-myth-or.html</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>8</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Work Friendships: How to Balance Office Friends and Professionalism</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/balancing-office-friendships-and.html</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>9</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Cryptocurrency Regulation: Is It Possible?</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/cryptocurrency-regulation-is-it-possible.html</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Day 22</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>10</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>How to Deal With Being Ignored</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/how-to-face-ignorance.html</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Signs You Need a Career Break (and How to Plan One)</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/its-time-to-take-break-sign-indicates.html</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>2</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Multitasking and Stress: How They Are Connected</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/multi-tasking-and-stress-unraveling.html</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>3</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Singapore Dollar: A Stable Currency in a Volatile World</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/singapore-dollar-stable-currency-in.html</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>4</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Sleep Hacks: How to Improve Your Sleep and Feel Refreshed</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/sleep-hacks-how-to-transform-your-sleep.html</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>5</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Digital Overload: The Impact of Constant Connectivity</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/the-digital-age-dilemma-exploring.html</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>6</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>What Is the Gig Economy? How It Works, Pros and Cons</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/the-rise-of-gig-economy-exploring.html</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>7</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Being Ignored in a Relationship: Causes and Solutions</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/understanding-ignorance-in-relationships.html</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>8</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Burnout at Work: How to Handle Work Pressure Without Burning Out</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/understanding-impact-of-work-pressure.html</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>9</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Behavioral Economics Explained: Key Principles</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/behavioral-economics.html</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Day 23</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>10</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Fooled by Randomness: Book Review and Key Lessons</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/book-review-fooled-by-randomness.html</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>How Does Google Make Money From Free Services?</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/how-google-provides-free-services.html</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>2</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Ikigai Meaning: The Japanese Concept of Purpose Explained</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/introduction-to-ikigai-exploring.html</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>3</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Letting Go of the Past: A Guide to Moving Forward</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/letting-go-of-past-guide-to-moving.html</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>4</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Parenting Challenges: Common Problems and How to Handle Them</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/parenting-challenges-addressing.html</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>5</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Toxic Boss: Signs of a Toxic Boss and Red Flags</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/recognizing-toxic-boss-behavior-signs.html</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>6</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Time Management Tips and Strategies for a Balanced Life</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/the-importance-of-balance-on-time.html</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>7</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>How Exercise Improves Mental Health</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/the-role-of-exercise-in-mental.html</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>8</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Zen Stories: The Tea Master's Lesson and Its Meaning</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/the-tea-masters-lesson-zen-story.html</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>9</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>The 5 Love Languages Explained</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/understanding-love-languages.html</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Day 24</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>10</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>How Does the Fed Control Inflation? The Federal Reserve's Role</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/11/the-role-of-federal-reserve-in.html</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Why Do Currencies Have Different Values in Different Countries?</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2023/11/why-currency-value-varies-with-each.html</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>2</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>How to Be Consistent: Habits That Stick</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2024/01/how-to-be-consistent.html</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>3</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Kokorozashi: The Japanese Art of Personal Mission</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2024/01/kokorozashi-cultivating-sense-of.html</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>4</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>The Power of Now: Book Summary and Key Lessons</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2024/01/the-power-of-now-brief-overview-of-book.html</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>5</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Australia Minimum Wage 2026: Tax, Mortgages and Pensions</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/australia-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>6</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Austria Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/austria-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>7</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Belgium Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/belgium-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>8</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Brazil Minimum Wage 2026: Mortgages and Pensions</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/brazil-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>9</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Canada Minimum Wage 2026: Tax, Mortgages and Pensions</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/canada-in-numbers-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Day 25</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>10</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>China Minimum Wage 2026: Mortgages and Pensions</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/china-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Czechia Minimum Wage 2026: Tax, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/czechia-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>2</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Denmark Minimum Wage 2026: Tax, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/denmark-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>3</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Estonia Minimum Wage 2026: Tax, Mortgages and Energy</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/estonia-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>4</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Finland Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/finland-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>5</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>France Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/france-in-numbers-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>6</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Germany Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/germany-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>7</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Greece Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/greece-in-numbers-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>8</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>India Minimum Wage 2026: Mortgages and Pensions</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/india-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>9</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Ireland Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/ireland-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Day 26</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>10</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Italy Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/italy-in-numbers-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Japan Minimum Wage 2026: Tax, Mortgages and Pensions</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/japan-in-numbers-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>2</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Latvia Minimum Wage 2026: Tax, Mortgages and Energy</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/latvia-in-numbers-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>3</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Lithuania Minimum Wage 2026: Tax, Mortgages and Energy</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/lithuania-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>4</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Luxembourg Minimum Wage 2026: Tax, Mortgages and Energy</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/luxembourg-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>5</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Mexico Minimum Wage 2026: Tax, Mortgages and Pensions</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/mexico-in-numbers-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>6</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>New Zealand Minimum Wage 2026: Tax and Pensions</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/new-zealand-in-numbers-2026-minimum.html</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>7</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Norway Minimum Wage 2026: Tax, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/norway-in-numbers-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>8</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Poland Minimum Wage 2026: Tax, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/poland-in-numbers-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>9</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Portugal Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/portugal-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Day 27</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>10</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Slovakia Minimum Wage 2026: Tax, Mortgages and Energy</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/slovakia-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>1</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Slovenia Minimum Wage 2026: Tax, Mortgages and Energy</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/slovenia-in-numbers-2026-minimum-wage.html</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>2</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>South Africa Minimum Wage 2026 and Pensions</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/south-africa-in-numbers-2026-minimum.html</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>3</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>South Korea Minimum Wage 2026: Tax and Pensions</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/south-korea-in-numbers-2026-minimum.html</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>4</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Spain Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/spain-in-numbers-2026-minimum-wage-tax.html</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>5</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Switzerland Income Tax 2026: Mortgages and Pensions</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/switzerland-in-numbers-2026-tax.html</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>6</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Netherlands Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/the-netherlands-in-numbers-2026-minimum.html</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>7</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>UK Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/the-united-kingdom-in-numbers-2026.html</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>8</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>US Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/the-united-states-in-numbers-2026.html</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>9</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Innocence Quotes: Strive for Brilliance Without Losing Your Innocence</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2025/10/spread-positivity.html</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Day 28</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>10</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Truth Quotes: Why Truth Gives You Freedom and Lies Bring Restlessness</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2025/10/spread-positivity_26.html</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Day 29</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>1</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>How to Find Inner Calm and Inner Peace: It Starts in Yourself</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>https://randomthoughtsever.blogspot.com/2025/10/today-thought.html</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1353,6 +6374,247 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId281"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seo/URL_INSPECTION.xlsx
+++ b/seo/URL_INSPECTION.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E282"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,8 @@
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +472,16 @@
           <t>Done?</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Google status (30 Oct)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Last crawled</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -482,12 +494,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reduce Image Size in KB Online Free: Every Photo and PDF Size</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/reduce-image-size-in-kb-online-free.html</t>
+          <t>https://randomthoughtsever.blogspot.com/</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -502,12 +525,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Compress PDF to 200KB Online Free (Scholarship and Exam Uploads)</t>
+          <t>KB to MB Converter (and MB to KB): Both 1,000 and 1,024 Answers</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-200kb-online-free.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/kb-to-mb-converter-and-mb-to-kb-both.html</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Redirect error</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -522,14 +556,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Resize Image to 20KB Online Free (Compress Photo to 20 KB)</t>
+          <t>Compress PDF to 100KB Online Free (Scans and Certificates)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-20kb-online-free.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-100kb-online-free-scans.html</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,14 +583,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Signature Resize Online Free: 10-20 KB for SSC, IBPS, PAN and NEET</t>
+          <t>Resize Image to 50KB Online Free (Photo Between 20 and 50 KB)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/signature-resize-online-free-10-20-kb.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-50kb-online-free-photo.html</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -562,14 +610,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Resize Photo for PAN Card Online Free (20 KB, 200 DPI, No Upload)</t>
+          <t>Resize Image to CM Online Free (cm, mm or Inches to Pixels)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-photo-for-pan-card-online-free.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-cm-online-free-cm-mm-or.html</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -582,14 +637,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KB to MB Converter (and MB to KB): Both 1,000 and 1,024 Answers</t>
+          <t>SSC Photo Resize and Exam Signature Resizer (UPSC, IBPS, NEET)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/kb-to-mb-converter-and-mb-to-kb-both.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/exam-photo-and-signature-resizer-exact.html</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -602,14 +664,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMI Calculator: Home Loan EMI With Prepayment Savings</t>
+          <t>Compress PDF to 2MB Online Free (Aadhaar Update, Job Portals)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/home-loan-emi-calculator-with.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-2mb-online-free-aadhaar.html</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -622,14 +691,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SIP Calculator: Estimate Your Mutual Fund Returns (With Step-Up)</t>
+          <t>Reduce Image Size in KB Online Free: Every Photo and PDF Size</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/sip-calculator-estimate-your-mutual.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/reduce-image-size-in-kb-online-free.html</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -642,14 +718,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Income Tax Calculator FY 2026-27: New vs Old Tax Regime</t>
+          <t>Compress PDF to 200KB Online Free (Scholarship and Exam Uploads)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/income-tax-calculator-fy-2026-27-new-vs.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-200kb-online-free.html</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -662,14 +745,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GST Calculator 2026: Add or Remove GST at 5%, 18% and 40%</t>
+          <t>Resize Image to 20KB Online Free (Compress Photo to 20 KB)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/gst-calculator-2026-add-or-remove-gst.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-20kb-online-free.html</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -682,14 +772,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Compress PDF to 100KB Online Free (Scans and Certificates)</t>
+          <t>Signature Resize Online Free: 10-20 KB for SSC, IBPS, PAN and NEET</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-100kb-online-free-scans.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/signature-resize-online-free-10-20-kb.html</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -702,14 +799,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Compress PDF to 500KB Online Free (GST, Job and Visa Uploads)</t>
+          <t>Resize Photo for PAN Card Online Free (20 KB, 200 DPI, No Upload)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-500kb-online-free-gst.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-photo-for-pan-card-online-free.html</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -722,14 +826,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Compress PDF to 300KB Online Free (NEET, UPSC, e-Visa, PAN)</t>
+          <t>Compress PDF to 500KB Online Free (GST, Job and Visa Uploads)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-300kb-online-free-neet.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-500kb-online-free-gst.html</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -742,14 +853,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Compress PDF to 1MB Online Free (Under 1 MB, No Upload)</t>
+          <t>Compress PDF to 300KB Online Free (NEET, UPSC, e-Visa, PAN)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-1mb-online-free-under-1.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-300kb-online-free-neet.html</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -762,14 +880,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Resize Image to 50KB Online Free (Photo Between 20 and 50 KB)</t>
+          <t>Compress PDF to 1MB Online Free (Under 1 MB, No Upload)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-50kb-online-free-photo.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-1mb-online-free-under-1.html</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -790,6 +915,13 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-100kb-online-free.html</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -810,6 +942,13 @@
           <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-200kb-online-free.html</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -822,14 +961,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Resize Image to CM Online Free (cm, mm or Inches to Pixels)</t>
+          <t>JPG to PDF Under 200KB Online Free (Also 100KB, 300KB, 500KB)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-cm-online-free-cm-mm-or.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/jpg-to-pdf-under-200kb-online-free-also.html</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -842,14 +988,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JPG to PDF Under 200KB Online Free (Also 100KB, 300KB, 500KB)</t>
+          <t>Masked Aadhaar: How to Mask Your Aadhaar or PAN Before Sharing (Free)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/jpg-to-pdf-under-200kb-online-free-also.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-mask-your-aadhaar-or-pan-before.html</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -862,14 +1015,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FD, RD, PPF, EPF and Sukanya Samriddhi Calculator (2026 Rates)</t>
+          <t>US Visa Photo Size and DV Lottery Photo: 600x600 Pixels, Under 240 KB</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/ppf-epf-sukanya-samriddhi-fd-and-rd.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/us-visa-and-dv-lottery-photo-600x600.html</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -882,14 +1042,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Free Passport Photo Maker: Exact Sizes for 8 Countries</t>
+          <t>How Much Cash Can You Take on a Plane? Limits for 53 Countries (2026)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/free-passport-and-visa-photo-maker.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-much-cash-can-i-carry-on.html</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -902,14 +1069,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SSC Photo Resize and Exam Signature Resizer (UPSC, IBPS, NEET)</t>
+          <t>Compress PDF to 50KB Online Free (Sharp Text, No Upload)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/exam-photo-and-signature-resizer-exact.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-50kb-online-free-sharp.html</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -922,14 +1096,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Merge PDF and Split PDF Free: Reorder Pages Without Uploading</t>
+          <t>Resize Image to 10KB Online Free (Photo or Signature Under 10 KB)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/merge-split-and-reorder-pdfs-free.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-10kb-online-free-photo.html</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -942,14 +1123,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Masked Aadhaar: How to Mask Your Aadhaar or PAN Before Sharing (Free)</t>
+          <t>Resize Image to 15KB Online Free (Photo Under 15 KB, No Upload)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-mask-your-aadhaar-or-pan-before.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-15kb-online-free-photo.html</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -962,14 +1150,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US Visa Photo Size and DV Lottery Photo: 600x600 Pixels, Under 240 KB</t>
+          <t>Resize Image to 30KB Online Free (Photo or Signature Under 30 KB)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/us-visa-and-dv-lottery-photo-600x600.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-30kb-online-free-photo.html</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -982,14 +1177,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEIC to JPG Converter: Shrink Photos and Remove Location, No Upload</t>
+          <t>Resize Image to 500KB Online Free (Compress JPG Under 500 KB)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/convert-heic-to-jpg-shrink-photos-and.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-500kb-online-free.html</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1002,14 +1204,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What Is a Good CIBIL Score? How to Check and Improve It</t>
+          <t>Compress PDF to 150KB Online Free (Private, No Upload)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/what-is-good-cibil-score-how-to-check.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-150kb-online-free.html</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1022,14 +1231,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>How Much Cash Can You Take on a Plane? Limits for 53 Countries (2026)</t>
+          <t>Traveling With Medication Internationally: What's Banned Where</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/how-much-cash-can-i-carry-on.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/can-i-take-codeine-sleeping-pills-or.html</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1042,14 +1258,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Compress PDF to 50KB Online Free (Sharp Text, No Upload)</t>
+          <t>Do I Pay Tax on Money Sent From Abroad? 31 Countries (2026)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-50kb-online-free-sharp.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/do-i-pay-tax-on-money-sent-from-abroad.html</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1062,14 +1285,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Compress PDF to 2MB Online Free (Aadhaar Update, Job Portals)</t>
+          <t>Australian Passport Photo Size: 35-40 x 45-50 mm (Free Maker)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-2mb-online-free-aadhaar.html</t>
-        </is>
-      </c>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/australian-passport-photo-size-35-40-x.html</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1082,12 +1312,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Resize Image to 10KB Online Free (Photo or Signature Under 10 KB)</t>
+          <t>EMI Calculator: Home Loan EMI With Prepayment Savings</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-10kb-online-free-photo.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/home-loan-emi-calculator-with.html</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1343,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Resize Image to 15KB Online Free (Photo Under 15 KB, No Upload)</t>
+          <t>SIP Calculator: Estimate Your Mutual Fund Returns (With Step-Up)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-15kb-online-free-photo.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/sip-calculator-estimate-your-mutual.html</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1374,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Resize Image to 30KB Online Free (Photo or Signature Under 30 KB)</t>
+          <t>Income Tax Calculator FY 2026-27: New vs Old Tax Regime</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-30kb-online-free-photo.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/income-tax-calculator-fy-2026-27-new-vs.html</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1405,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Resize Image to 500KB Online Free (Compress JPG Under 500 KB)</t>
+          <t>GST Calculator 2026: Add or Remove GST at 5%, 18% and 40%</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/resize-image-to-500kb-online-free.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/gst-calculator-2026-add-or-remove-gst.html</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1436,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Compress PDF to 150KB Online Free (Private, No Upload)</t>
+          <t>FD, RD, PPF, EPF and Sukanya Samriddhi Calculator (2026 Rates)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/compress-pdf-to-150kb-online-free.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/ppf-epf-sukanya-samriddhi-fd-and-rd.html</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1467,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Traveling With Medication Internationally: What's Banned Where</t>
+          <t>Free Passport Photo Maker: Exact Sizes for 8 Countries</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/can-i-take-codeine-sleeping-pills-or.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/free-passport-and-visa-photo-maker.html</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1498,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Do I Pay Tax on Money Sent From Abroad? 31 Countries (2026)</t>
+          <t>Merge PDF and Split PDF Free: Reorder Pages Without Uploading</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/do-i-pay-tax-on-money-sent-from-abroad.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/merge-split-and-reorder-pdfs-free.html</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1529,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>How Much Emergency Fund Do You Need? (With Calculator)</t>
+          <t>HEIC to JPG Converter: Shrink Photos and Remove Location, No Upload</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/how-much-emergency-fund-do-you-need.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/convert-heic-to-jpg-shrink-photos-and.html</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1560,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Free Resume Maker With a Free PDF Download (No Paywall)</t>
+          <t>What Is a Good CIBIL Score? How to Check and Improve It</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/free-resume-builder-with-free-pdf.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/what-is-good-cibil-score-how-to-check.html</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1591,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Free UPI QR Code Generator: Scan-and-Pay Poster That Never Expires</t>
+          <t>Free Resume Maker With a Free PDF Download (No Paywall)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/free-upi-qr-code-generator-make-scan.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/free-resume-builder-with-free-pdf.html</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1282,15 +1622,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Australian Passport Photo Size: 35-40 x 45-50 mm (Free Maker)</t>
+          <t>Free UPI QR Code Generator: Scan-and-Pay Poster That Never Expires</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/australian-passport-photo-size-35-40-x.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/free-upi-qr-code-generator-make-scan.html</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1303,15 +1653,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cheapest Countries to Retire Abroad on $2,000 a Month</t>
+          <t>Canadian Passport Photo Size: 50x70 mm Rules (Free Photo Maker)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/best-countries-to-retire-abroad-on-2000.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/canadian-passport-photo-size-50x70-mm.html</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1324,15 +1680,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Canadian Passport Photo Size: 50x70 mm Rules (Free Photo Maker)</t>
+          <t>Lump Sum or Monthly Pension: Which Should You Take? (Calculator)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/canadian-passport-photo-size-50x70-mm.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/lump-sum-or-monthly-pension-which.html</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1345,15 +1707,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Career Guide: Work Smarter, Avoid Burnout and Grow (Start Here)</t>
+          <t>OCI Photo Size: Square JPEG Under 200 KB (Free Photo Maker)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/career-guide-work-smarter-avoid-burnout.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/oci-photo-size-square-jpeg-under-200-kb.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1366,15 +1734,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Visa Photo Size: 33x48 mm and 354x472 Digital (Free Maker)</t>
+          <t>UK Passport Photo Size: 35x45 mm Print and Digital Rules (Free)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/china-visa-photo-size-33x48-mm-and.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/uk-passport-photo-size-35x45-mm-print.html</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1387,15 +1761,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Compare Countries 2026: Wages, Tax, Mortgages and Pensions</t>
+          <t>US Passport Photo Requirements and Size: Make a 2x2 Photo Free at Home</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/compare-countries-2026-minimum-wage-tax.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/us-passport-photo-size-and-rules-make.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1408,15 +1788,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Credit Card Payoff Calculator: How Long Will Your Debt Take?</t>
+          <t>Corporate Life Lessons: The Biggest Lessons From the Corporate World</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/credit-card-payoff-calculator-how-long.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/what-are-biggest-lessons-you-have.html</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1429,15 +1815,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Debt Consolidation Loans: When They Save Money (Calculator)</t>
+          <t>What Is Karma? Meaning, Types and How It Works</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/debt-consolidation-loans-when-they-save.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/what-is-karma.html</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1450,15 +1842,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Free Invoice Generator: No Sign-Up, No Watermark, PDF in Seconds</t>
+          <t>Why Is Dubai Called A Fake City?</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/free-invoice-generator-no-sign-up-no.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/why-is-dubai-called-fake-city.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1471,15 +1869,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Free Online Tools That Don't Upload Your Files or Need Sign-Up</t>
+          <t>What Makes You Age Faster? The Worst Habits That Age You</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/free-online-tools-that-dont-upload-your.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/the-worst-habits-that-age-you-what-you.html</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1492,15 +1896,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Free QR Code Generator That Never Expires (No Sign-Up, No Trial)</t>
+          <t>Is Data Science a Good Career? Why It Is the Next Big Thing in Jobs</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/free-qr-code-generator-that-never.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/why-data-science-is-emerging-field-next.html</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1513,15 +1923,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Life Insurance Calculator: How Much Does Life Insurance Cost by Age?</t>
+          <t>How to Increase Focus and Concentration</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/how-much-does-life-insurance-cost-by.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/how-to-increase-focus-and-concentration.html</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1534,15 +1950,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Prediction Markets: How Kalshi and Polymarket Work and Are They Legal?</t>
+          <t>Biological Neural Network Explained (vs Artificial Neural Networks)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/how-prediction-markets-like-kalshi-and.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/02/a-study-about-biological-neural-network.html</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1555,15 +1977,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>How to Buy SpaceX Stock and Other IPO Shares as a Small Investor</t>
+          <t>The Power of Positivity: How Positive Thinking Helps</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/how-small-investors-can-buy-ipo-shares.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/understanding-power-of-positivity.html</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1576,15 +2004,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>How Much Car Can I Afford? Car Affordability Calculator for 2026</t>
+          <t>How to Be Consistent: Habits That Stick</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-afford-car-in-2026-when-average.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2024/01/how-to-be-consistent.html</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1597,15 +2031,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>How to Explain a Gap in Employment or a Layoff in an Interview</t>
+          <t>Canada Minimum Wage 2026: Tax, Mortgages and Pensions</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-explain-layoff-or-career-gap-in.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/canada-in-numbers-2026-minimum-wage-tax.html</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1618,15 +2058,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sign PDF Free: How to Sign a PDF Without an Account or Limits</t>
+          <t>Ireland Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-sign-pdf-for-free-without.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/ireland-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1639,15 +2085,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Income Tax by Country 2026: Countries With the Lowest Income Tax</t>
+          <t>Italy Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/income-tax-by-country-2026-how-much-of.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/italy-in-numbers-2026-minimum-wage-tax.html</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1660,15 +2112,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Countries With No Inheritance Tax and Rates by Country 2026</t>
+          <t>Slovakia Minimum Wage 2026: Tax, Mortgages and Energy</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/inheritance-tax-by-country-2026.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/slovakia-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>URL is unknown to Google</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1681,15 +2139,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Will Interest Rates Go Up? 7 Money Moves to Make Now</t>
+          <t>Cheapest Countries to Retire Abroad on $2,000 a Month</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/interest-rates-are-rising-again-7-money.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/best-countries-to-retire-abroad-on-2000.html</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1702,15 +2166,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gold Price Fall 2026: Is Gold Still a Safe Haven?</t>
+          <t>China Visa Photo Size: 33x48 mm and 354x472 Digital (Free Maker)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/is-gold-still-safe-haven-after-its-big.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/china-visa-photo-size-33x48-mm-and.html</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1723,15 +2193,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Electric Car vs Petrol Cost: Is an EV Cheaper to Run? (Calculator)</t>
+          <t>Free QR Code Generator That Never Expires (No Sign-Up, No Trial)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/is-it-cheaper-to-charge-ev-or-fill-up.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/free-qr-code-generator-that-never.html</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1744,15 +2220,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>What Jobs Will AI Replace in 2026, and Which Skills Keep You Safe?</t>
+          <t>Countries With No Inheritance Tax and Rates by Country 2026</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/jobs-ai-is-replacing-in-2026-and-skills.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/inheritance-tax-by-country-2026.html</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1765,15 +2247,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lump Sum or Monthly Pension: Which Should You Take? (Calculator)</t>
+          <t>Will Interest Rates Go Up? 7 Money Moves to Make Now</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/lump-sum-or-monthly-pension-which.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/interest-rates-are-rising-again-7-money.html</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1786,15 +2274,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Meeting Time Zone Planner: Find a Time That Works in Every City</t>
+          <t>What Jobs Will AI Replace in 2026, and Which Skills Keep You Safe?</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/meeting-time-zone-planner-find-time.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/jobs-ai-is-replacing-in-2026-and-skills.html</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1807,15 +2301,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Self-Improvement and Mental Well-Being: A Practical Guide (Start Here)</t>
+          <t>Meeting Time Zone Planner: Find a Time That Works in Every City</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/mental-well-being-and-self-improvement.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/meeting-time-zone-planner-find-time.html</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1828,15 +2328,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minimum Wage by Country 2026: Hourly and Monthly Rates in US Dollars</t>
+          <t>Mortgage Rates by Country 2026: Where Buying a Home Costs the Most</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/minimum-wage-by-country-2026-hourly-and.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/mortgage-rates-by-country-2026-where.html</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1849,15 +2355,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mortgage Rates by Country 2026: Where Buying a Home Costs the Most</t>
+          <t>Salary Increase 2027 Forecasts by Country: Every Major Survey</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/mortgage-rates-by-country-2026-where.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/salary-increase-forecasts-2027-by.html</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1870,15 +2382,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OCI Photo Size: Square JPEG Under 200 KB (Free Photo Maker)</t>
+          <t>Schengen Visa Photo Size: 35x45 mm, Face 32-36 mm (Free Photo Maker)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/oci-photo-size-square-jpeg-under-200-kb.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/schengen-visa-photo-size-35x45-mm-face.html</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1891,15 +2409,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Personal Finance for Beginners: A Step-by-Step Guide (Start Here)</t>
+          <t>Average Pension by Country 2026: State Pension Amounts Compared</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/personal-finance-for-beginners-step-by.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/state-pension-amounts-by-country-2026.html</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1912,15 +2436,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Retirement Age by Country 2026, Including Retirement Age in Europe</t>
+          <t>Character Counter and Word Counter With Limits for X, LinkedIn and SMS</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/retirement-age-by-country-2026-state.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/word-counter-with-character-limits-for.html</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1933,15 +2463,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salary Increase 2027 Forecasts by Country: Every Major Survey</t>
+          <t>How to Become a Fashion Designer: A Career Guide</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/salary-increase-forecasts-2027-by.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/fashion-designing.html</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1954,15 +2490,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Schengen Visa Photo Size: 35x45 mm, Face 32-36 mm (Free Photo Maker)</t>
+          <t>Financial Independence: How to Achieve It Step by Step</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/schengen-visa-photo-size-35x45-mm-face.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/financial-independence.html</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1975,15 +2517,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rent or Buy? Rent vs Buy Calculator With Mortgage Rates Above 7%</t>
+          <t>What Are Altcoins? Alternative Cryptocurrencies Explained</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/should-you-buy-house-with-mortgage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/what-are-altcoins.html</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1996,15 +2544,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Stablecoins Explained: Can You Earn Interest on Digital Dollars?</t>
+          <t>USA vs UK: Which Country Is Better to Live In?</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/stablecoins-explained-can-you-really.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/which-is-better-to-live-in-usa-or-uk.html</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2017,15 +2571,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Average Pension by Country 2026: State Pension Amounts Compared</t>
+          <t>FIRE Movement: Financial Independence, Retire Early Explained</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/state-pension-amounts-by-country-2026.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/financial-independence-retire-earlyfire.html</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2038,15 +2598,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Strong Password and Passphrase Generator, Plus a Safe Breach Check</t>
+          <t>How to Increase Positive Thoughts: Practical Tips</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/strong-password-and-passphrase.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/how-to-increase-positive-thoughts.html</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2059,15 +2625,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Subscription Tracker: Find Forgotten Subscriptions Before They Renew</t>
+          <t>What Is Inflation? Causes, Types and Effects Explained</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/subscription-tracker-find-forgotten.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/inflation-tutorial.html</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2080,15 +2652,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UK Passport Photo Size: 35x45 mm Print and Digital Rules (Free)</t>
+          <t>Qualities of a Good Team Leader</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/uk-passport-photo-size-35x45-mm-print.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/qualities-of-good-team-lead.html</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2101,15 +2679,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US Passport Photo Requirements and Size: Make a 2x2 Photo Free at Home</t>
+          <t>Oxford University Facts: Lesser-Known Facts About Oxford</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/us-passport-photo-size-and-rules-make.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/unknown-facts-of-university-of-oxford.html</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2122,15 +2706,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>What Happens If a Bank Fails? Your Money if a Bank or App Goes Bust</t>
+          <t>How to Control Your Emotions: Practical Tips</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/what-happens-to-your-money-if-your-bank.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/08/how-to-control-emotions.html</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2143,15 +2733,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Digital Legacy: Your Online Accounts and Crypto When You Die</t>
+          <t>How to Manage Credit Card Debt Wisely</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/what-happens-to-your-online-accounts.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/08/how-to-manage-credit-card-loans.html</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2164,15 +2760,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raise Calculator: What Is a Fair Pay Raise in 2026 After Inflation?</t>
+          <t>Bitcoin Crash: Why Bitcoin Prices Fall</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/what-is-fair-pay-raise-in-2026-how-to.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/08/what-is-bitcoin-crash.html</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2185,15 +2787,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>What Is GDP? Its Role in Measuring an Economy, Explained</t>
+          <t>Floating Interest Rate Home Loan: Is a Floating Rate Good for You?</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/what-is-gdp-its-role-in-measuring.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/is-floating-interest-is-good-for-house.html</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2206,15 +2814,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Best Place to Keep Cash When Rates Rise: Savings, T-Bills or Funds</t>
+          <t>Is Investing in Gold a Good Idea?</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/where-to-keep-your-cash-when-rates-rise.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/is-invest-in-gold-is-good-idea.html</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2227,15 +2841,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Why Are Groceries and Prices So Expensive When Inflation Is Down?</t>
+          <t>What Is a 401(k) and How Does It Work? A Complete Guide</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/why-are-prices-still-so-high-when.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/a-comprehensive-guide-401k.html</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2248,15 +2868,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Why Did My Car Insurance Go Up When I Never Made a Claim?</t>
+          <t>Can Money Really Buy Happiness?</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/why-did-my-insurance-premium-go-up-when.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/can-money-really-buy-happiness-what-can.html</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2269,15 +2895,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10-Year Treasury Yield Above 5%: Why, and What It Means for You</t>
+          <t>Data Structures: Why They Matter in Programming</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/why-is-10-year-treasury-yield-above-5.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/data-structures-why-it-matters-and-how.html</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2290,15 +2922,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Credit Karma vs FICO: Why Is My Credit Score Different on Every App?</t>
+          <t>Hedging in Finance: A Complete Guide</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/why-is-my-credit-score-different-on.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/hedging-in-financea-comprehensive-guide.html</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2311,15 +2949,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Character Counter and Word Counter With Limits for X, LinkedIn and SMS</t>
+          <t>How Does Google Search Work? The Algorithm Behind the Results</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/word-counter-with-character-limits-for.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/how-googles-algorithm-works-science.html</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2332,15 +2976,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CEO vs COO: Roles, Responsibilities and Key Differences</t>
+          <t>When to Quit Your Job: 6 Signs It Is Time</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/ceo-vs-coo.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/the-6-signs-you-need-to-quit-your-job.html</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2353,15 +3003,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>How the Election System in India Works</t>
+          <t>Annuities Explained: What You Need to Know</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/election-system-in-india.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/the-ultimate-guide-to-annuities-what.html</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2374,15 +3030,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>How US Elections Work: The Election System Explained Simply</t>
+          <t>Dealing With Uncertainty: How to Cope When Things Are Unclear</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/election-system-in-united-states.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/uncertainty-isnt-always-bad-thing-how.html</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2395,15 +3057,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>How to Become a Fashion Designer: A Career Guide</t>
+          <t>Why Politics Is Important: The Biggest Myths</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/fashion-designing.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/why-politics-is-important-biggest-myths.html</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2416,15 +3084,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Financial Independence: How to Achieve It Step by Step</t>
+          <t>Life Lessons to Learn Before Age 30</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/financial-independence.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/12/lessons-should-be-learned-before-age-30.html</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2437,15 +3111,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>How Do You Know When Someone Really Loves You?</t>
+          <t>Why Is French Important? What French Means to the World</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/how-do-you-know-when-someone-really.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/12/what-does-french-language-mean-to-world.html</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2458,15 +3138,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>How to Be Happy: Simple Habits for a Happier Life</t>
+          <t>Morning Routine for More Energy: Simple Steps for an Energetic Morning</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-be-happy.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/do-these-steps-to-have-energetic-morning.html</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2479,15 +3165,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>How to Control Diabetes Naturally: Diet and Lifestyle Tips</t>
+          <t>New Year Resolutions: How to Actually Keep Them, Step by Step</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-control-diabetes.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/step-to-step-process-to-achieve-new.html</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2500,15 +3192,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>How to Get Over Someone and Move On After a Breakup</t>
+          <t>Healthy Lifestyle Tips: Simple Steps to Improve Your Lifestyle</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-forgot-someone.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/steps-to-improve-your-lifestyle.html</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2521,15 +3219,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>How to Stop Being Shy: Overcoming Shyness as an Introvert</t>
+          <t>How to Be Successful in Life: 20 Steps to Win</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-overcome-introvert-shyness.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/steps-to-win-in-life.html</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2542,15 +3246,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>How to Fall Asleep Fast: Simple Ways to Sleep Peacefully</t>
+          <t>Ways to Raise Smarter Children</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-sleep-fastly-and-peacefully.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/ways-to-raise-your-children-as-smarter.html</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2563,15 +3273,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Is Fate Real? Destiny vs Free Will Explained</t>
+          <t>How to Be a Good Leader: 12 Rules of Leadership</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/is-fate-is-true.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2022/02/grammar-of-good-leader.html</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2584,15 +3300,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lesser-Known Facts About Joe Biden</t>
+          <t>Reconnaissance in Ethical Hacking: Footprinting Explained</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/unknown-facts-of-joe-biden.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/02/reconnaissance-in-ethical-hacking.html</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2605,15 +3327,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>What Are Altcoins? Alternative Cryptocurrencies Explained</t>
+          <t>Service Based Companies vs Product Based Companies: The Difference</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/what-are-altcoins.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/a-study-about-service-and-product-based.html</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2626,15 +3354,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Corporate Life Lessons: The Biggest Lessons From the Corporate World</t>
+          <t>Effects of a Recession: How It Affects You and the Economy</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/what-are-biggest-lessons-you-have.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/a-study-on-recession-impact.html</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2647,15 +3381,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>What Is Karma? Meaning, Types and How It Works</t>
+          <t>Forex Trading Explained: A Beginner's Guide</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/what-is-karma.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/forex-study.html</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2668,15 +3408,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Australia vs Canada: Which Is Better to Live In?</t>
+          <t>How Is Currency Value Determined? How a Country's Currency Is Valued</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/which-is-better-country-to-live-in.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/how-currency-value-of-country-been.html</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2689,15 +3435,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA vs UK: Which Country Is Better to Live In?</t>
+          <t>NASDAQ 100 vs S&amp;P 500: Which Is Better?</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/which-is-better-to-live-in-usa-or-uk.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/nasdaq-100-vs-s-500.html</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2710,15 +3462,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Why Is Dubai Called A Fake City?</t>
+          <t>Why Is Bitcoin Banned? Why Governments Ban or Restrict Bitcoin</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/why-is-dubai-called-fake-city.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/reasons-on-why-governments-ban-bitcoins.html</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2731,15 +3489,21 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Why Is the US So Rich? Why America Is Wealthier Than Other Countries</t>
+          <t>What Happens When a Bank Fails?</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/06/why-is-united-states-of-america-so-much.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/what-happen-when-bank-fails.html</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2752,15 +3516,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Deep Work vs Shallow Work: How to Focus Better</t>
+          <t>Product Based Companies: What They Are and How They Work</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/07/deep-work-vs-shallow-work.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-about-product-based-companies.html</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2773,15 +3543,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FIRE Movement: Financial Independence, Retire Early Explained</t>
+          <t>Fixed vs Floating Interest Rate: Which Is Better?</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/07/financial-independence-retire-earlyfire.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-fixed-interest-vs-floating.html</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2794,15 +3570,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>How to Increase Positive Thoughts: Practical Tips</t>
+          <t>Tax Free Countries: Countries With No Income Tax</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/07/how-to-increase-positive-thoughts.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-tax-free-nations.html</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2815,15 +3597,21 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>How to Learn Anything Fast: Proven Techniques</t>
+          <t>How to Reduce Stress at Work: Easing Mental Stress</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/07/how-to-learn-anything-fast.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/how-to-reduce-mental-stress-at-work.html</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2836,15 +3624,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Workplace Relationships: How to Keep Good Relations at Work</t>
+          <t>Is Online Education Good or Bad?</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/07/how-to-maintain-good-relation-in-work.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/is-online-education-is-good-or-bad.html</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2857,15 +3651,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>What Is Inflation? Causes, Types and Effects Explained</t>
+          <t>Reducing Mental Stress: Strategies for a Healthier Mind</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/07/inflation-tutorial.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/05/reducing-mental-stress-strategies-for.html</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2878,15 +3678,21 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Mutual Funds vs Stocks and Day Trading: Which Is Better?</t>
+          <t>Developing vs Developed Countries: Key Differences</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/07/mutual-funds-vs-stocks.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/classification-of-nations-developing-vs.html</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2899,15 +3705,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Qualities of a Good Team Leader</t>
+          <t>How to Practice Mindfulness: A Beginner's Guide</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/07/qualities-of-good-team-lead.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/how-to-attain-mindfulness.html</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2920,15 +3732,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Oxford University Facts: Lesser-Known Facts About Oxford</t>
+          <t>How to Pay Off Credit Card Debt Fast</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/07/unknown-facts-of-university-of-oxford.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/methods-to-efficiently-pay-off-credit.html</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2941,15 +3759,21 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>How to Control Your Emotions: Practical Tips</t>
+          <t>Constructive Criticism in Leadership: Why It Matters</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/08/how-to-control-emotions.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/the-essential-role-of-constructive.html</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2962,15 +3786,21 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>How to Manage Credit Card Debt Wisely</t>
+          <t>Surround Yourself With Good People: Why Leaders Need Worthy People</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/08/how-to-manage-credit-card-loans.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/the-leaders-alliance-with-worthy-men.html</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2983,15 +3813,21 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>What Is IQ? Intelligence Quotient Explained</t>
+          <t>Why Do Companies Manufacture in China and East Asia?</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/08/intelligence-quotient-blog.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/why-developed-countries-want-to-open.html</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3004,15 +3840,21 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Is Investing in Cryptocurrency Safe?</t>
+          <t>Cost of Living Around the World: A Comparison</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/08/is-invest-in-cryptocurrency-is-safe.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/07/cost-of-living-comparison-across-world.html</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3025,15 +3867,21 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bitcoin Crash: Why Bitcoin Prices Fall</t>
+          <t>How to Turn Thoughts Into Action</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/08/what-is-bitcoin-crash.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/bridging-gap-transforming-thoughts-into.html</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3046,15 +3894,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Artificial Intelligence vs Machine Learning: Key Differences</t>
+          <t>The Psychology of Fear: How the Brain Responds</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/09/comparing-artificial-intelligence-vs.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/the-psychology-of-fear-understanding.html</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3067,15 +3921,21 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>How Much Does Google Know About You?</t>
+          <t>World Reserve Currency: Why the US Dollar Holds the Title</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/09/how-much-does-google-know-about-me.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/the-us-dollar-global-reserve-currency.html</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3088,15 +3948,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Standard Deduction 2026 and Other US Tax Deductions Explained</t>
+          <t>What Does It Take to Be Courageous?</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/09/income-tax-exemptions-in-united-states.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/what-it-takes-to-be-courage.html</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3109,15 +3975,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Floating Interest Rate Home Loan: Is a Floating Rate Good for You?</t>
+          <t>Work-Life Balance: Balancing Ambition and Well-Being</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/09/is-floating-interest-is-good-for-house.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/work-life-balance-navigating.html</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3130,15 +4002,21 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Is Investing in Gold a Good Idea?</t>
+          <t>Artificial Superintelligence: Myth or Inevitable Reality?</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/09/is-invest-in-gold-is-good-idea.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/artificial-superintelligence-myth-or.html</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3151,15 +4029,21 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SIP vs Lumpsum: Which Is Better in Mutual Funds?</t>
+          <t>Singapore Dollar: A Stable Currency in a Volatile World</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/09/lumpsum-vs-sip-mutual-fund-which-is-best.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/singapore-dollar-stable-currency-in.html</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3172,15 +4056,21 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>What Is Mature Love? The Definition of Mature Love, Explained</t>
+          <t>Behavioral Economics Explained: Key Principles</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/09/what-is-mature-love-definition-of.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/behavioral-economics.html</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3193,15 +4083,21 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>What Is a 401(k) and How Does It Work? A Complete Guide</t>
+          <t>Fooled by Randomness: Book Review and Key Lessons</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/a-comprehensive-guide-401k.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/book-review-fooled-by-randomness.html</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3214,15 +4110,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>What Is an Alpha Male? Traits and Myths</t>
+          <t>Ikigai Meaning: The Japanese Concept of Purpose Explained</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/all-about-alpha-male.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/introduction-to-ikigai-exploring.html</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3235,15 +4137,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Can Money Really Buy Happiness?</t>
+          <t>Parenting Challenges: Common Problems and How to Handle Them</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/can-money-really-buy-happiness-what-can.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/parenting-challenges-addressing.html</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3256,15 +4164,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Data Structures: Why They Matter in Programming</t>
+          <t>Time Management Tips and Strategies for a Balanced Life</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/data-structures-why-it-matters-and-how.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/the-importance-of-balance-on-time.html</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3277,15 +4191,21 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hedging in Finance: A Complete Guide</t>
+          <t>The 5 Love Languages Explained</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/hedging-in-financea-comprehensive-guide.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/understanding-love-languages.html</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3298,15 +4218,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>How Does Google Search Work? The Algorithm Behind the Results</t>
+          <t>How Does the Fed Control Inflation? The Federal Reserve's Role</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/how-googles-algorithm-works-science.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/11/the-role-of-federal-reserve-in.html</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3319,15 +4245,21 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Compassion Fatigue: Signs, Causes and How to Recover</t>
+          <t>Why Do Currencies Have Different Values in Different Countries?</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/how-to-cure-compassion-fatigue-guide-to.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/11/why-currency-value-varies-with-each.html</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3340,15 +4272,21 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Behavioral Finance and Investor Psychology Explained</t>
+          <t>Kokorozashi: The Japanese Art of Personal Mission</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/investor-psychology-behavioral-finance.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2024/01/kokorozashi-cultivating-sense-of.html</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3361,15 +4299,21 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>When to Quit Your Job: 6 Signs It Is Time</t>
+          <t>The Power of Now: Book Summary and Key Lessons</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/the-6-signs-you-need-to-quit-your-job.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2024/01/the-power-of-now-brief-overview-of-book.html</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3382,15 +4326,21 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annuities Explained: What You Need to Know</t>
+          <t>Australia Minimum Wage 2026: Tax, Mortgages and Pensions</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/the-ultimate-guide-to-annuities-what.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/australia-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3403,15 +4353,21 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>What Makes You Age Faster? The Worst Habits That Age You</t>
+          <t>Austria Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/the-worst-habits-that-age-you-what-you.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/austria-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3424,15 +4380,21 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Dealing With Uncertainty: How to Cope When Things Are Unclear</t>
+          <t>Belgium Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/uncertainty-isnt-always-bad-thing-how.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/belgium-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3445,15 +4407,21 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>What Is a Wormhole in Space? Explained Simply</t>
+          <t>Brazil Minimum Wage 2026: Mortgages and Pensions</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/what-is-warm-hole-in-space-just-what.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/brazil-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3466,15 +4434,21 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Is Data Science a Good Career? Why It Is the Next Big Thing in Jobs</t>
+          <t>Estonia Minimum Wage 2026: Tax, Mortgages and Energy</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/why-data-science-is-emerging-field-next.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/estonia-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3487,15 +4461,21 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Why Politics Is Important: The Biggest Myths</t>
+          <t>Greece Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/10/why-politics-is-important-biggest-myths.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/greece-in-numbers-2026-minimum-wage-tax.html</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3508,15 +4488,21 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Life Lessons to Learn Before Age 30</t>
+          <t>Lithuania Minimum Wage 2026: Tax, Mortgages and Energy</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/12/lessons-should-be-learned-before-age-30.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/lithuania-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3529,15 +4515,21 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Mental Toughness: How to Build Unbreakable Inner Strength</t>
+          <t>Luxembourg Minimum Wage 2026: Tax, Mortgages and Energy</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/12/the-mental-toughness-guide-how-to.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/luxembourg-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3550,15 +4542,21 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Why Is French Important? What French Means to the World</t>
+          <t>Mexico Minimum Wage 2026: Tax, Mortgages and Pensions</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2021/12/what-does-french-language-mean-to-world.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/mexico-in-numbers-2026-minimum-wage-tax.html</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3571,15 +4569,21 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Morning Routine for More Energy: Simple Steps for an Energetic Morning</t>
+          <t>New Zealand Minimum Wage 2026: Tax and Pensions</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2022/01/do-these-steps-to-have-energetic-morning.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/new-zealand-in-numbers-2026-minimum.html</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3592,15 +4596,21 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>How to Increase Your Chances of Success: Zen Quotes</t>
+          <t>Norway Minimum Wage 2026: Tax, Pensions and Energy</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2022/01/how-to-increase-chances-of-success-zen.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/norway-in-numbers-2026-minimum-wage-tax.html</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3613,15 +4623,21 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>How to Increase Focus and Concentration</t>
+          <t>Poland Minimum Wage 2026: Tax, Pensions and Energy</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2022/01/how-to-increase-focus-and-concentration.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/poland-in-numbers-2026-minimum-wage-tax.html</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3634,15 +4650,21 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>New Year Resolutions: How to Actually Keep Them, Step by Step</t>
+          <t>US Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2022/01/step-to-step-process-to-achieve-new.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/the-united-states-in-numbers-2026.html</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3655,15 +4677,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Healthy Lifestyle Tips: Simple Steps to Improve Your Lifestyle</t>
+          <t>Innocence Quotes: Strive for Brilliance Without Losing Your Innocence</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2022/01/steps-to-improve-your-lifestyle.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2025/10/spread-positivity.html</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3676,15 +4704,21 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>How to Be Successful in Life: 20 Steps to Win</t>
+          <t>Truth Quotes: Why Truth Gives You Freedom and Lies Bring Restlessness</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2022/01/steps-to-win-in-life.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2025/10/spread-positivity_26.html</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3697,15 +4731,21 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ways to Raise Smarter Children</t>
+          <t>How to Find Inner Calm and Inner Peace: It Starts in Yourself</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2022/01/ways-to-raise-your-children-as-smarter.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2025/10/today-thought.html</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Discovered - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3718,15 +4758,25 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>How to Be a Good Leader: 12 Rules of Leadership</t>
+          <t>Career Guide: Work Smarter, Avoid Burnout and Grow (Start Here)</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2022/02/grammar-of-good-leader.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/career-guide-work-smarter-avoid-burnout.html</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3739,15 +4789,25 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>How to Become Rich: The Habits That Really Build Wealth</t>
+          <t>Compare Countries 2026: Wages, Tax, Mortgages and Pensions</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2022/09/top-secrets-to-become-rich.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/compare-countries-2026-minimum-wage-tax.html</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3760,15 +4820,25 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Biological Neural Network Explained (vs Artificial Neural Networks)</t>
+          <t>Free Invoice Generator: No Sign-Up, No Watermark, PDF in Seconds</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/02/a-study-about-biological-neural-network.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/free-invoice-generator-no-sign-up-no.html</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3781,15 +4851,25 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Reconnaissance in Ethical Hacking: Footprinting Explained</t>
+          <t>Free Online Tools That Don't Upload Your Files or Need Sign-Up</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/02/reconnaissance-in-ethical-hacking.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/free-online-tools-that-dont-upload-your.html</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3802,15 +4882,25 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Service Based Companies vs Product Based Companies: The Difference</t>
+          <t>Life Insurance Calculator: How Much Does Life Insurance Cost by Age?</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/03/a-study-about-service-and-product-based.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-much-does-life-insurance-cost-by.html</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3823,15 +4913,25 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Effects of a Recession: How It Affects You and the Economy</t>
+          <t>Prediction Markets: How Kalshi and Polymarket Work and Are They Legal?</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/03/a-study-on-recession-impact.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-prediction-markets-like-kalshi-and.html</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3844,15 +4944,25 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Forex Trading Explained: A Beginner's Guide</t>
+          <t>How to Buy SpaceX Stock and Other IPO Shares as a Small Investor</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/03/forex-study.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-small-investors-can-buy-ipo-shares.html</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3865,15 +4975,25 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>How Is Currency Value Determined? How a Country's Currency Is Valued</t>
+          <t>How Much Car Can I Afford? Car Affordability Calculator for 2026</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/03/how-currency-value-of-country-been.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-afford-car-in-2026-when-average.html</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3886,15 +5006,25 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>How to Find a Job in the UAE: A Complete Guide</t>
+          <t>How to Explain a Gap in Employment or a Layoff in an Interview</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/03/how-to-find-job-in-united-arab-emirates.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-explain-layoff-or-career-gap-in.html</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3907,15 +5037,25 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>How to Socialize: Tips to Connect With People</t>
+          <t>Sign PDF Free: How to Sign a PDF Without an Account or Limits</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/03/how-to-socialize.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/how-to-sign-pdf-for-free-without.html</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3928,15 +5068,25 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>NASDAQ 100 vs S&amp;P 500: Which Is Better?</t>
+          <t>Income Tax by Country 2026: Countries With the Lowest Income Tax</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/03/nasdaq-100-vs-s-500.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/income-tax-by-country-2026-how-much-of.html</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3949,15 +5099,25 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Why Is Bitcoin Banned? Why Governments Ban or Restrict Bitcoin</t>
+          <t>Electric Car vs Petrol Cost: Is an EV Cheaper to Run? (Calculator)</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/03/reasons-on-why-governments-ban-bitcoins.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/is-it-cheaper-to-charge-ev-or-fill-up.html</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3970,15 +5130,25 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Time Zones Explained: How They Work</t>
+          <t>Minimum Wage by Country 2026: Hourly and Monthly Rates in US Dollars</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/03/time-zones-study.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/minimum-wage-by-country-2026-hourly-and.html</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3991,15 +5161,25 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>What Happens When a Bank Fails?</t>
+          <t>Personal Finance for Beginners: A Step-by-Step Guide (Start Here)</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/03/what-happen-when-bank-fails.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/personal-finance-for-beginners-step-by.html</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4012,15 +5192,25 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Product Based Companies: What They Are and How They Work</t>
+          <t>Retirement Age by Country 2026, Including Retirement Age in Europe</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-about-product-based-companies.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/retirement-age-by-country-2026-state.html</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4033,15 +5223,25 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Fixed vs Floating Interest Rate: Which Is Better?</t>
+          <t>Rent or Buy? Rent vs Buy Calculator With Mortgage Rates Above 7%</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-fixed-interest-vs-floating.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/should-you-buy-house-with-mortgage.html</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4054,15 +5254,25 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Is an MBA Worth It? A Complete Guide</t>
+          <t>Stablecoins Explained: Can You Earn Interest on Digital Dollars?</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-mba.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/stablecoins-explained-can-you-really.html</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4075,15 +5285,25 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tax Free Countries: Countries With No Income Tax</t>
+          <t>Strong Password and Passphrase Generator, Plus a Safe Breach Check</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-tax-free-nations.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/strong-password-and-passphrase.html</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4096,15 +5316,25 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Zen Quotes and Sayings: Classic Zen Quotes and Their Meaning</t>
+          <t>Subscription Tracker: Find Forgotten Subscriptions Before They Renew</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-zen-quotes.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/subscription-tracker-find-forgotten.html</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4117,15 +5347,25 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>How to Diversify Your Stock Portfolio</t>
+          <t>Digital Legacy: Your Online Accounts and Crypto When You Die</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/04/how-to-do-portfolio-diversification-in.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/what-happens-to-your-online-accounts.html</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4138,15 +5378,25 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Life Satisfaction: How to Be More Satisfied With Your Life</t>
+          <t>Raise Calculator: What Is a Fair Pay Raise in 2026 After Inflation?</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/04/how-to-improve-my-self-satisfaction.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/what-is-fair-pay-raise-in-2026-how-to.html</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4159,15 +5409,25 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>How to Reduce Stress at Work: Easing Mental Stress</t>
+          <t>What Is GDP? Its Role in Measuring an Economy, Explained</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/04/how-to-reduce-mental-stress-at-work.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/what-is-gdp-its-role-in-measuring.html</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4180,15 +5440,25 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Is Online Education Good or Bad?</t>
+          <t>Best Place to Keep Cash When Rates Rise: Savings, T-Bills or Funds</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/04/is-online-education-is-good-or-bad.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/where-to-keep-your-cash-when-rates-rise.html</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4201,15 +5471,25 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Finland Education System: Why It Is Considered the Best</t>
+          <t>10-Year Treasury Yield Above 5%: Why, and What It Means for You</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/04/why-finland-education-system-is.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/why-is-10-year-treasury-yield-above-5.html</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4222,15 +5502,25 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Reducing Mental Stress: Strategies for a Healthier Mind</t>
+          <t>Credit Karma vs FICO: Why Is My Credit Score Different on Every App?</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/05/reducing-mental-stress-strategies-for.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/why-is-my-credit-score-different-on.html</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4243,15 +5533,25 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Developing vs Developed Countries: Key Differences</t>
+          <t>CEO vs COO: Roles, Responsibilities and Key Differences</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/classification-of-nations-developing-vs.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/ceo-vs-coo.html</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4264,15 +5564,25 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Living in the Present Moment: How to Live in the Present</t>
+          <t>How the Election System in India Works</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/embracing-present-art-of-living-in.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/election-system-in-india.html</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4285,15 +5595,25 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>How to Deal With Rejection: Building Resilience</t>
+          <t>How US Elections Work: The Election System Explained Simply</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/embracing-resilience-strategies-to-face.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/election-system-in-united-states.html</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4306,15 +5626,25 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>How to Practice Mindfulness: A Beginner's Guide</t>
+          <t>How Do You Know When Someone Really Loves You?</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/how-to-attain-mindfulness.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-do-you-know-when-someone-really.html</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4327,15 +5657,25 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>How to Cope With Losing Your Job</t>
+          <t>How to Be Happy: Simple Habits for a Happier Life</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/how-to-face-job-termination.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-be-happy.html</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4348,15 +5688,25 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>How to Pay Off Credit Card Debt Fast</t>
+          <t>How to Control Diabetes Naturally: Diet and Lifestyle Tips</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/methods-to-efficiently-pay-off-credit.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-control-diabetes.html</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4369,15 +5719,25 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Benefits of Working From Home: Why Professionals Love It</t>
+          <t>How to Get Over Someone and Move On After a Breakup</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/the-enchantment-of-work-from-home.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-forgot-someone.html</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4390,15 +5750,25 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Constructive Criticism in Leadership: Why It Matters</t>
+          <t>How to Stop Being Shy: Overcoming Shyness as an Introvert</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/the-essential-role-of-constructive.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-overcome-introvert-shyness.html</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4411,15 +5781,25 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Surround Yourself With Good People: Why Leaders Need Worthy People</t>
+          <t>How to Fall Asleep Fast: Simple Ways to Sleep Peacefully</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/the-leaders-alliance-with-worthy-men.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/how-to-sleep-fastly-and-peacefully.html</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4432,15 +5812,25 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>The Psychology of Losing Money in the Stock Market</t>
+          <t>Is Fate Real? Destiny vs Free Will Explained</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/the-psychology-of-losing-money-in-stock.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/is-fate-is-true.html</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4453,15 +5843,25 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Benefits of AI for Business: Why Companies Invest in AI</t>
+          <t>Lesser-Known Facts About Joe Biden</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/the-significance-of-artificial.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/unknown-facts-of-joe-biden.html</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4474,15 +5874,25 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Why Do Companies Manufacture in China and East Asia?</t>
+          <t>Australia vs Canada: Which Is Better to Live In?</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/why-developed-countries-want-to-open.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/06/which-is-better-country-to-live-in.html</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4495,15 +5905,25 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>How to Avoid Online Scams and Not Lose Money</t>
+          <t>Deep Work vs Shallow Work: How to Focus Better</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/06/write-various-headings-for-how-to-dont.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/deep-work-vs-shallow-work.html</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4516,15 +5936,25 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Breaking the Burnout Cycle: Work-Life Balance Tips</t>
+          <t>How to Learn Anything Fast: Proven Techniques</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/07/breaking-burnout-cycle-strategies-for.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/how-to-learn-anything-fast.html</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4537,15 +5967,25 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Cost of Living Around the World: A Comparison</t>
+          <t>Workplace Relationships: How to Keep Good Relations at Work</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/07/cost-of-living-comparison-across-world.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/how-to-maintain-good-relation-in-work.html</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4558,15 +5998,25 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>From Casual to Serious: Moving a Relationship Forward</t>
+          <t>Mutual Funds vs Stocks and Day Trading: Which Is Better?</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/07/navigating-transition-from-casual-to.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/07/mutual-funds-vs-stocks.html</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4579,15 +6029,25 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bad Boss Signs: How to Tell You Work for a Toxic Boss</t>
+          <t>What Is IQ? Intelligence Quotient Explained</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/07/recognizing-telltale-signs-of-working.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/08/intelligence-quotient-blog.html</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4600,15 +6060,25 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Unconditional Love: What It Means and How to Cultivate It</t>
+          <t>Is Investing in Cryptocurrency Safe?</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/07/unconditional-love-what-it-means-and.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/08/is-invest-in-cryptocurrency-is-safe.html</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4621,15 +6091,25 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>How to Turn Thoughts Into Action</t>
+          <t>Artificial Intelligence vs Machine Learning: Key Differences</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/bridging-gap-transforming-thoughts-into.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/comparing-artificial-intelligence-vs.html</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4642,15 +6122,25 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>FIRE Movement: Financial Independence, Retire Early Explained</t>
+          <t>How Much Does Google Know About You?</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/fire-financial-independence-retire.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/how-much-does-google-know-about-me.html</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4663,15 +6153,25 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Do Violent Movies Cause Violence? What the Research Says</t>
+          <t>Standard Deduction 2026 and Other US Tax Deductions Explained</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/lights-camera-action-and-reaction-link.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/income-tax-exemptions-in-united-states.html</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4684,15 +6184,25 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portfolio Diversification Strategies for Long-Term Success</t>
+          <t>SIP vs Lumpsum: Which Is Better in Mutual Funds?</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/mastering-financial-portfolio.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/lumpsum-vs-sip-mutual-fund-which-is-best.html</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4705,15 +6215,25 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Love in the Digital Age: How Technology Changes Love</t>
+          <t>What Is Mature Love? The Definition of Mature Love, Explained</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/normal-0-false-false-false-en-in-x-none.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/09/what-is-mature-love-definition-of.html</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4726,15 +6246,25 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Pursuit of Happiness: Strategies for a Fulfilling Life</t>
+          <t>What Is an Alpha Male? Traits and Myths</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/pursuit-of-happiness-strategies-for.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/all-about-alpha-male.html</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4747,15 +6277,25 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>How to Become Indispensable at Work and Strengthen Your Position</t>
+          <t>Compassion Fatigue: Signs, Causes and How to Recover</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/strengthening-your-position-in-your-job.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/how-to-cure-compassion-fatigue-guide-to.html</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4768,15 +6308,25 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Qualities of a Good Leader: The Leadership Qualities That Matter Most</t>
+          <t>Behavioral Finance and Investor Psychology Explained</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/the-desired-qualities-of-leadership.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/investor-psychology-behavioral-finance.html</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4789,15 +6339,25 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>What Is the Petrodollar? The Petrodollar System Explained</t>
+          <t>What Is a Wormhole in Space? Explained Simply</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/the-genesis-of-petrodollars-unveiling.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/10/what-is-warm-hole-in-space-just-what.html</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4810,15 +6370,25 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>The Psychology of Fear: How the Brain Responds</t>
+          <t>Mental Toughness: How to Build Unbreakable Inner Strength</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/the-psychology-of-fear-understanding.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2021/12/the-mental-toughness-guide-how-to.html</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4831,15 +6401,25 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>The Psychology of Love: What Makes Love Last</t>
+          <t>How to Increase Your Chances of Success: Zen Quotes</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/the-psychology-of-long-lasting-love.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2022/01/how-to-increase-chances-of-success-zen.html</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4852,15 +6432,25 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>World Reserve Currency: Why the US Dollar Holds the Title</t>
+          <t>How to Become Rich: The Habits That Really Build Wealth</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/the-us-dollar-global-reserve-currency.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2022/09/top-secrets-to-become-rich.html</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4873,15 +6463,25 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>The Power of Positivity: How Positive Thinking Helps</t>
+          <t>How to Find a Job in the UAE: A Complete Guide</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/understanding-power-of-positivity.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/how-to-find-job-in-united-arab-emirates.html</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4894,15 +6494,25 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Understanding Stress: The First Step to a Stress-Free Life</t>
+          <t>How to Socialize: Tips to Connect With People</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/understanding-stress-first-step-to.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/how-to-socialize.html</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4915,15 +6525,25 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>What Does It Take to Be Courageous?</t>
+          <t>Time Zones Explained: How They Work</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/what-it-takes-to-be-courage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/03/time-zones-study.html</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4936,15 +6556,25 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Work-Life Balance: Balancing Ambition and Well-Being</t>
+          <t>Is an MBA Worth It? A Complete Guide</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/work-life-balance-navigating.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/a-study-on-mba.html</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4957,15 +6587,25 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>What Is Zen? Zen Buddhism, Mindfulness and Enlightenment Explained</t>
+          <t>How to Diversify Your Stock Portfolio</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/08/zen-journey-into-essence-of-mindfulness.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/how-to-do-portfolio-diversification-in.html</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4978,15 +6618,25 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Artificial Superintelligence: Myth or Inevitable Reality?</t>
+          <t>Life Satisfaction: How to Be More Satisfied With Your Life</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/artificial-superintelligence-myth-or.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/how-to-improve-my-self-satisfaction.html</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4999,15 +6649,25 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Work Friendships: How to Balance Office Friends and Professionalism</t>
+          <t>Finland Education System: Why It Is Considered the Best</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/balancing-office-friendships-and.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/04/why-finland-education-system-is.html</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5020,15 +6680,25 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cryptocurrency Regulation: Is It Possible?</t>
+          <t>Living in the Present Moment: How to Live in the Present</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/cryptocurrency-regulation-is-it-possible.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/embracing-present-art-of-living-in.html</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5041,15 +6711,25 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>How to Deal With Being Ignored</t>
+          <t>How to Deal With Rejection: Building Resilience</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/how-to-face-ignorance.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/embracing-resilience-strategies-to-face.html</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5062,15 +6742,25 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Signs You Need a Career Break (and How to Plan One)</t>
+          <t>How to Cope With Losing Your Job</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/its-time-to-take-break-sign-indicates.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/how-to-face-job-termination.html</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5083,15 +6773,25 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Multitasking and Stress: How They Are Connected</t>
+          <t>Benefits of Working From Home: Why Professionals Love It</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/multi-tasking-and-stress-unraveling.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/the-enchantment-of-work-from-home.html</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5104,15 +6804,25 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Singapore Dollar: A Stable Currency in a Volatile World</t>
+          <t>The Psychology of Losing Money in the Stock Market</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/singapore-dollar-stable-currency-in.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/the-psychology-of-losing-money-in-stock.html</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5125,15 +6835,25 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Sleep Hacks: How to Improve Your Sleep and Feel Refreshed</t>
+          <t>Benefits of AI for Business: Why Companies Invest in AI</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/sleep-hacks-how-to-transform-your-sleep.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/the-significance-of-artificial.html</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5146,15 +6866,25 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Digital Overload: The Impact of Constant Connectivity</t>
+          <t>How to Avoid Online Scams and Not Lose Money</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/the-digital-age-dilemma-exploring.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/06/write-various-headings-for-how-to-dont.html</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5167,15 +6897,25 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>What Is the Gig Economy? How It Works, Pros and Cons</t>
+          <t>Breaking the Burnout Cycle: Work-Life Balance Tips</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/the-rise-of-gig-economy-exploring.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/07/breaking-burnout-cycle-strategies-for.html</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5188,15 +6928,25 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Being Ignored in a Relationship: Causes and Solutions</t>
+          <t>From Casual to Serious: Moving a Relationship Forward</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/understanding-ignorance-in-relationships.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/07/navigating-transition-from-casual-to.html</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5209,15 +6959,25 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Burnout at Work: How to Handle Work Pressure Without Burning Out</t>
+          <t>Unconditional Love: What It Means and How to Cultivate It</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/09/understanding-impact-of-work-pressure.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/07/unconditional-love-what-it-means-and.html</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5230,15 +6990,25 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Behavioral Economics Explained: Key Principles</t>
+          <t>FIRE Movement: Financial Independence, Retire Early Explained</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/behavioral-economics.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/fire-financial-independence-retire.html</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5251,15 +7021,25 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Fooled by Randomness: Book Review and Key Lessons</t>
+          <t>Do Violent Movies Cause Violence? What the Research Says</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/book-review-fooled-by-randomness.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/lights-camera-action-and-reaction-link.html</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5272,15 +7052,25 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>How Does Google Make Money From Free Services?</t>
+          <t>Portfolio Diversification Strategies for Long-Term Success</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/how-google-provides-free-services.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/mastering-financial-portfolio.html</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5293,15 +7083,25 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Ikigai Meaning: The Japanese Concept of Purpose Explained</t>
+          <t>Love in the Digital Age: How Technology Changes Love</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/introduction-to-ikigai-exploring.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/normal-0-false-false-false-en-in-x-none.html</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5314,15 +7114,25 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Letting Go of the Past: A Guide to Moving Forward</t>
+          <t>How to Become Indispensable at Work and Strengthen Your Position</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/letting-go-of-past-guide-to-moving.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/strengthening-your-position-in-your-job.html</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5335,15 +7145,25 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Parenting Challenges: Common Problems and How to Handle Them</t>
+          <t>Qualities of a Good Leader: The Leadership Qualities That Matter Most</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/parenting-challenges-addressing.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/the-desired-qualities-of-leadership.html</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5356,15 +7176,25 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Toxic Boss: Signs of a Toxic Boss and Red Flags</t>
+          <t>What Is the Petrodollar? The Petrodollar System Explained</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/recognizing-toxic-boss-behavior-signs.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/the-genesis-of-petrodollars-unveiling.html</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5377,15 +7207,25 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Time Management Tips and Strategies for a Balanced Life</t>
+          <t>The Psychology of Love: What Makes Love Last</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/the-importance-of-balance-on-time.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/the-psychology-of-long-lasting-love.html</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5398,15 +7238,25 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>How Exercise Improves Mental Health</t>
+          <t>Understanding Stress: The First Step to a Stress-Free Life</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/the-role-of-exercise-in-mental.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/understanding-stress-first-step-to.html</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5419,15 +7269,25 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Zen Stories: The Tea Master's Lesson and Its Meaning</t>
+          <t>What Is Zen? Zen Buddhism, Mindfulness and Enlightenment Explained</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/the-tea-masters-lesson-zen-story.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/08/zen-journey-into-essence-of-mindfulness.html</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5440,15 +7300,25 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>The 5 Love Languages Explained</t>
+          <t>Work Friendships: How to Balance Office Friends and Professionalism</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/10/understanding-love-languages.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/balancing-office-friendships-and.html</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5461,15 +7331,25 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>How Does the Fed Control Inflation? The Federal Reserve's Role</t>
+          <t>Signs You Need a Career Break (and How to Plan One)</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/11/the-role-of-federal-reserve-in.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/its-time-to-take-break-sign-indicates.html</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5482,15 +7362,25 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Why Do Currencies Have Different Values in Different Countries?</t>
+          <t>Multitasking and Stress: How They Are Connected</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2023/11/why-currency-value-varies-with-each.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/multi-tasking-and-stress-unraveling.html</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5503,15 +7393,25 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>How to Be Consistent: Habits That Stick</t>
+          <t>Digital Overload: The Impact of Constant Connectivity</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2024/01/how-to-be-consistent.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/the-digital-age-dilemma-exploring.html</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5524,15 +7424,25 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Kokorozashi: The Japanese Art of Personal Mission</t>
+          <t>What Is the Gig Economy? How It Works, Pros and Cons</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2024/01/kokorozashi-cultivating-sense-of.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/the-rise-of-gig-economy-exploring.html</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5545,15 +7455,25 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>The Power of Now: Book Summary and Key Lessons</t>
+          <t>Being Ignored in a Relationship: Causes and Solutions</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2024/01/the-power-of-now-brief-overview-of-book.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/understanding-ignorance-in-relationships.html</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5566,15 +7486,25 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Australia Minimum Wage 2026: Tax, Mortgages and Pensions</t>
+          <t>Burnout at Work: How to Handle Work Pressure Without Burning Out</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/australia-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/09/understanding-impact-of-work-pressure.html</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5587,15 +7517,25 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Austria Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+          <t>How Does Google Make Money From Free Services?</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/austria-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/how-google-provides-free-services.html</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5608,15 +7548,25 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Belgium Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+          <t>Letting Go of the Past: A Guide to Moving Forward</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/belgium-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/letting-go-of-past-guide-to-moving.html</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5629,15 +7579,25 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Brazil Minimum Wage 2026: Mortgages and Pensions</t>
+          <t>Toxic Boss: Signs of a Toxic Boss and Red Flags</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/brazil-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/recognizing-toxic-boss-behavior-signs.html</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5650,15 +7610,25 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Canada Minimum Wage 2026: Tax, Mortgages and Pensions</t>
+          <t>How Exercise Improves Mental Health</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/canada-in-numbers-2026-minimum-wage-tax.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/the-role-of-exercise-in-mental.html</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5671,15 +7641,25 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>China Minimum Wage 2026: Mortgages and Pensions</t>
+          <t>Zen Stories: The Tea Master's Lesson and Its Meaning</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/china-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2023/10/the-tea-masters-lesson-zen-story.html</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5692,15 +7672,25 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Czechia Minimum Wage 2026: Tax, Pensions and Energy</t>
+          <t>China Minimum Wage 2026: Mortgages and Pensions</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/czechia-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/china-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5713,15 +7703,25 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Denmark Minimum Wage 2026: Tax, Pensions and Energy</t>
+          <t>Czechia Minimum Wage 2026: Tax, Pensions and Energy</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/denmark-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/czechia-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5734,15 +7734,25 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Estonia Minimum Wage 2026: Tax, Mortgages and Energy</t>
+          <t>Denmark Minimum Wage 2026: Tax, Pensions and Energy</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/estonia-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/denmark-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5764,6 +7774,16 @@
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5776,15 +7796,25 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>France Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+          <t>Germany Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/france-in-numbers-2026-minimum-wage-tax.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/germany-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5797,15 +7827,25 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Germany Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+          <t>India Minimum Wage 2026: Mortgages and Pensions</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/germany-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/india-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5818,15 +7858,25 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Greece Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+          <t>Japan Minimum Wage 2026: Tax, Mortgages and Pensions</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/greece-in-numbers-2026-minimum-wage-tax.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/japan-in-numbers-2026-minimum-wage-tax.html</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5839,15 +7889,25 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>India Minimum Wage 2026: Mortgages and Pensions</t>
+          <t>Latvia Minimum Wage 2026: Tax, Mortgages and Energy</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/india-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/latvia-in-numbers-2026-minimum-wage-tax.html</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5860,15 +7920,25 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Ireland Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+          <t>Portugal Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/ireland-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/portugal-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5881,15 +7951,25 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
+          <t>Slovenia Minimum Wage 2026: Tax, Mortgages and Energy</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/italy-in-numbers-2026-minimum-wage-tax.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/slovenia-in-numbers-2026-minimum-wage.html</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5902,15 +7982,25 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Japan Minimum Wage 2026: Tax, Mortgages and Pensions</t>
+          <t>South Africa Minimum Wage 2026 and Pensions</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/japan-in-numbers-2026-minimum-wage-tax.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/south-africa-in-numbers-2026-minimum.html</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5923,15 +8013,25 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Latvia Minimum Wage 2026: Tax, Mortgages and Energy</t>
+          <t>South Korea Minimum Wage 2026: Tax and Pensions</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/latvia-in-numbers-2026-minimum-wage-tax.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/south-korea-in-numbers-2026-minimum.html</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5944,15 +8044,25 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Lithuania Minimum Wage 2026: Tax, Mortgages and Energy</t>
+          <t>Spain Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/lithuania-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/spain-in-numbers-2026-minimum-wage-tax.html</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5965,15 +8075,25 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Luxembourg Minimum Wage 2026: Tax, Mortgages and Energy</t>
+          <t>Switzerland Income Tax 2026: Mortgages and Pensions</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/luxembourg-in-numbers-2026-minimum-wage.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/switzerland-in-numbers-2026-tax.html</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5986,15 +8106,25 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Mexico Minimum Wage 2026: Tax, Mortgages and Pensions</t>
+          <t>Netherlands Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/mexico-in-numbers-2026-minimum-wage-tax.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/the-netherlands-in-numbers-2026-minimum.html</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6007,330 +8137,25 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>New Zealand Minimum Wage 2026: Tax and Pensions</t>
+          <t>UK Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/new-zealand-in-numbers-2026-minimum.html</t>
+          <t>https://randomthoughtsever.blogspot.com/2026/10/the-united-kingdom-in-numbers-2026.html</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>Day 27</t>
-        </is>
-      </c>
-      <c r="B268" t="n">
-        <v>7</v>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Norway Minimum Wage 2026: Tax, Pensions and Energy</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/norway-in-numbers-2026-minimum-wage-tax.html</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Day 27</t>
-        </is>
-      </c>
-      <c r="B269" t="n">
-        <v>8</v>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Poland Minimum Wage 2026: Tax, Pensions and Energy</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/poland-in-numbers-2026-minimum-wage-tax.html</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>Day 27</t>
-        </is>
-      </c>
-      <c r="B270" t="n">
-        <v>9</v>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Portugal Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/portugal-in-numbers-2026-minimum-wage.html</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>Day 27</t>
-        </is>
-      </c>
-      <c r="B271" t="n">
-        <v>10</v>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Slovakia Minimum Wage 2026: Tax, Mortgages and Energy</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/slovakia-in-numbers-2026-minimum-wage.html</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B272" t="n">
-        <v>1</v>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Slovenia Minimum Wage 2026: Tax, Mortgages and Energy</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/slovenia-in-numbers-2026-minimum-wage.html</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B273" t="n">
-        <v>2</v>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>South Africa Minimum Wage 2026 and Pensions</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/south-africa-in-numbers-2026-minimum.html</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>3</v>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>South Korea Minimum Wage 2026: Tax and Pensions</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/south-korea-in-numbers-2026-minimum.html</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B275" t="n">
-        <v>4</v>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Spain Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/spain-in-numbers-2026-minimum-wage-tax.html</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B276" t="n">
-        <v>5</v>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Switzerland Income Tax 2026: Mortgages and Pensions</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/switzerland-in-numbers-2026-tax.html</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B277" t="n">
-        <v>6</v>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Netherlands Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
-        </is>
-      </c>
-      <c r="D277" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/the-netherlands-in-numbers-2026-minimum.html</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B278" t="n">
-        <v>7</v>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>UK Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
-        </is>
-      </c>
-      <c r="D278" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/the-united-kingdom-in-numbers-2026.html</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B279" t="n">
-        <v>8</v>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>US Minimum Wage 2026: Tax, Mortgages, Pensions and Energy</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2026/10/the-united-states-in-numbers-2026.html</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B280" t="n">
-        <v>9</v>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Innocence Quotes: Strive for Brilliance Without Losing Your Innocence</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2025/10/spread-positivity.html</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>Day 28</t>
-        </is>
-      </c>
-      <c r="B281" t="n">
-        <v>10</v>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Truth Quotes: Why Truth Gives You Freedom and Lies Bring Restlessness</t>
-        </is>
-      </c>
-      <c r="D281" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2025/10/spread-positivity_26.html</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>Day 29</t>
-        </is>
-      </c>
-      <c r="B282" t="n">
-        <v>1</v>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>How to Find Inner Calm and Inner Peace: It Starts in Yourself</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
-        <is>
-          <t>https://randomthoughtsever.blogspot.com/2025/10/today-thought.html</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Crawled - currently not indexed</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6600,21 +8425,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId265"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId281"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
